--- a/agriculture 27.xlsx
+++ b/agriculture 27.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t xml:space="preserve"> Production Statistics of Banana in Kerala  (1998-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">(Production in Tonnes)</t>
   </si>
@@ -155,6 +152,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -172,16 +170,16 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -270,11 +268,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -315,8 +313,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.62"/>
@@ -340,137 +338,165 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="B4" s="5" t="n">
+        <v>1.73403114950501</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-8.87937022458902</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.677267373380452</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>20.5875806810594</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.78236667265217</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-48.5480330913389</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.00484097400397232</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>-3.82652333837074</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>-2.47975147009875</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.65330280018186</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>-3.18966028339361</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>37.9539684870864</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>8.35637850186366</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>-6.88448074679113</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.73403114950501</v>
+        <v>-15.2844923763481</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-8.87937022458902</v>
+        <v>-34.8685046372761</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-0.677267373380452</v>
+        <v>-20.8182626741773</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>20.5875806810594</v>
+        <v>-23.6987818383167</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>7.78236667265217</v>
+        <v>-15.567106490737</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-48.5480330913389</v>
+        <v>1.49302707136998</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.00484097400397232</v>
+        <v>-22.8311386522076</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-3.82652333837074</v>
+        <v>-40.2947018885825</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-2.47975147009875</v>
+        <v>-23.4389517795855</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>9.65330280018186</v>
+        <v>-25.5796812137219</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-3.18966028339361</v>
+        <v>-5.07685712535979</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>37.9539684870864</v>
+        <v>2.72839262086901</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>8.35637850186366</v>
+        <v>-8.81047492232579</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>-6.88448074679113</v>
+        <v>-3.24675324675324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -478,46 +504,46 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-15.2844923763481</v>
+        <v>-0.226807140766749</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-34.8685046372761</v>
+        <v>20.9402126206964</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-20.8182626741773</v>
+        <v>13.6213868503819</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-23.6987818383167</v>
+        <v>-18.4325108853411</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-15.567106490737</v>
+        <v>1.93764798737175</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.49302707136998</v>
+        <v>7.1128354348529</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-22.8311386522076</v>
+        <v>21.2358845671267</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-40.2947018885825</v>
+        <v>-13.7898500347602</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-23.4389517795855</v>
+        <v>63.5649891024371</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-25.5796812137219</v>
+        <v>15.2092274678111</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-5.07685712535979</v>
+        <v>-3.81290322580645</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>2.72839262086901</v>
+        <v>11.4246376597036</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>-8.81047492232579</v>
+        <v>7.90946702360671</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>-3.24675324675324</v>
+        <v>-24.1492994230543</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -525,46 +551,46 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-0.226807140766749</v>
+        <v>22.7469384762044</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>20.9402126206964</v>
+        <v>17.7096774193548</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>13.6213868503819</v>
+        <v>21.1955447175905</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-18.4325108853411</v>
+        <v>13.1376037959668</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.93764798737175</v>
+        <v>25.3261584917347</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7.1128354348529</v>
+        <v>2.6863869604588</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>21.2358845671267</v>
+        <v>21.1021992238034</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-13.7898500347602</v>
+        <v>15.0509763262485</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>63.5649891024371</v>
+        <v>-1.56872246028982</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>15.2092274678111</v>
+        <v>21.66383093042</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-3.81290322580645</v>
+        <v>11.610436649004</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>11.4246376597036</v>
+        <v>3.58604379251701</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>7.90946702360671</v>
+        <v>14.3437077131259</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>-24.1492994230543</v>
+        <v>19.3728655696989</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -572,46 +598,46 @@
         <v>21</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>22.7469384762044</v>
+        <v>12.7426966963379</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>17.7096774193548</v>
+        <v>-16.5798848999726</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>21.1955447175905</v>
+        <v>-1.73473272064821</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>13.1376037959668</v>
+        <v>-2.56880733944954</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>25.3261584917347</v>
+        <v>-6.37259444598894</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.6863869604588</v>
+        <v>6.35655496766607</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>21.1021992238034</v>
+        <v>18.2903901209247</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>15.0509763262485</v>
+        <v>-6.61860418544107</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-1.56872246028982</v>
+        <v>14.7234828090147</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>21.66383093042</v>
+        <v>4.82695676495268</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>11.610436649004</v>
+        <v>3.4014423076923</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>3.58604379251701</v>
+        <v>2.82056873132126</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>14.3437077131259</v>
+        <v>-0.606508875739642</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>19.3728655696989</v>
+        <v>-5.43563068920676</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -619,46 +645,46 @@
         <v>22</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>12.7426966963379</v>
+        <v>-16.2621873675286</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-16.5798848999726</v>
+        <v>-2.41458607095927</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-1.73473272064821</v>
+        <v>-2.27448810182623</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-2.56880733944954</v>
+        <v>0.215227333871404</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-6.37259444598894</v>
+        <v>-1.46156384031673</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6.35655496766607</v>
+        <v>-20.8318938713466</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>18.2903901209247</v>
+        <v>-6.31784275832175</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-6.61860418544107</v>
+        <v>6.93759382371864</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>14.7234828090147</v>
+        <v>15.4298970178073</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4.82695676495268</v>
+        <v>0.74708608341525</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3.4014423076923</v>
+        <v>8.79925607346275</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>2.82056873132126</v>
+        <v>34.753374416806</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>-0.606508875739642</v>
+        <v>9.58475963685073</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>-5.43563068920676</v>
+        <v>-10.519801980198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -666,46 +692,46 @@
         <v>23</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-16.2621873675286</v>
+        <v>12.5988736315889</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-2.41458607095927</v>
+        <v>8.11311227066152</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-2.27448810182623</v>
+        <v>31.9553768616569</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.215227333871404</v>
+        <v>5.4228187919463</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-1.46156384031673</v>
+        <v>-3.51558576355174</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-20.8318938713466</v>
+        <v>21.1642520509687</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-6.31784275832175</v>
+        <v>-7.64040178141087</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>6.93759382371864</v>
+        <v>26.7672716334102</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>15.4298970178073</v>
+        <v>-3.99614325708909</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.74708608341525</v>
+        <v>-2.43790248390064</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>8.79925607346275</v>
+        <v>-16.6399572649573</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>34.753374416806</v>
+        <v>6.60890012127271</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>9.58475963685073</v>
+        <v>24.6412241387116</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>-10.519801980198</v>
+        <v>9.57430459505149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -713,46 +739,46 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>12.5988736315889</v>
+        <v>-14.9432392941441</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>8.11311227066152</v>
+        <v>-8.32944107115056</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>31.9553768616569</v>
+        <v>-7.96069006952193</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5.4228187919463</v>
+        <v>9.75299210593328</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-3.51558576355174</v>
+        <v>-16.7782905923587</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>21.1642520509687</v>
+        <v>5.55355470719585</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-7.64040178141087</v>
+        <v>25.0532292405962</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>26.7672716334102</v>
+        <v>4.52837650781095</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-3.99614325708909</v>
+        <v>-2.90042713841463</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-2.43790248390064</v>
+        <v>-0.294315145800295</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-16.6399572649573</v>
+        <v>-1.20474206984941</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>6.60890012127271</v>
+        <v>-23.528134769017</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>24.6412241387116</v>
+        <v>-8.74618625599303</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>9.57430459505149</v>
+        <v>4.97896213183731</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -760,46 +786,46 @@
         <v>25</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>-14.9432392941441</v>
+        <v>-13.0558308556326</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-8.32944107115056</v>
+        <v>11.7951766304348</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-7.96069006952193</v>
+        <v>-5.48794703221895</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>9.75299210593328</v>
+        <v>-5.52204176334107</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-16.7782905923587</v>
+        <v>18.7682428488033</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5.55355470719585</v>
+        <v>27.8354033028525</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>25.0532292405962</v>
+        <v>-17.311544368031</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>4.52837650781095</v>
+        <v>-24.8429814604616</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-2.90042713841463</v>
+        <v>16.0892754779054</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>-0.294315145800295</v>
+        <v>-25.6322810838695</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-1.20474206984941</v>
+        <v>-2.83453330738794</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-23.528134769017</v>
+        <v>2.68210980525747</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>-8.74618625599303</v>
+        <v>-42.8713580640026</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>4.97896213183731</v>
+        <v>2.92585170340682</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,46 +833,46 @@
         <v>26</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>-13.0558308556326</v>
+        <v>43.3087620639866</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>11.7951766304348</v>
+        <v>-5.53740979870869</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-5.48794703221895</v>
+        <v>-22.4716329551061</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-5.52204176334107</v>
+        <v>-6.92534381139489</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>18.7682428488033</v>
+        <v>-3.75662675982165</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>27.8354033028525</v>
+        <v>26.3118560828484</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-17.311544368031</v>
+        <v>22.6860730363163</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-24.8429814604616</v>
+        <v>26.3391059202577</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>16.0892754779054</v>
+        <v>10.8451324108763</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-25.6322810838695</v>
+        <v>-7.92693500838166</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-2.83453330738794</v>
+        <v>-29.7196261682243</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>2.68210980525747</v>
+        <v>-27.8556183440786</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>-42.8713580640026</v>
+        <v>26.7470215286003</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.92585170340682</v>
+        <v>-58.0607476635514</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -854,46 +880,46 @@
         <v>27</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>43.3087620639866</v>
+        <v>-8.52688514158447</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-5.53740979870869</v>
+        <v>9.5529109038276</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-22.4716329551061</v>
+        <v>7.28603245307031</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-6.92534381139489</v>
+        <v>14.0369393139842</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-3.75662675982165</v>
+        <v>-6.26345164702878</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>26.3118560828484</v>
+        <v>-17.564026709492</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>22.6860730363163</v>
+        <v>-3.27108185931715</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>26.3391059202577</v>
+        <v>-22.4776856869621</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>10.8451324108763</v>
+        <v>-22.4598101878753</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-7.92693500838166</v>
+        <v>-4.59349168149</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-29.7196261682243</v>
+        <v>5.45212765957446</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-27.8556183440786</v>
+        <v>9.79337196112695</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>26.7470215286003</v>
+        <v>2.46262093227791</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>-58.0607476635514</v>
+        <v>14.9798823893532</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -901,46 +927,46 @@
         <v>28</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>-8.52688514158447</v>
+        <v>-5.80935652173913</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9.5529109038276</v>
+        <v>16.7211832061069</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>7.28603245307031</v>
+        <v>-3.19516014234875</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>14.0369393139842</v>
+        <v>20.3692503470616</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-6.26345164702878</v>
+        <v>-1.57817948318804</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-17.564026709492</v>
+        <v>19.2729570388599</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-3.27108185931715</v>
+        <v>1.96046234711758</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-22.4776856869621</v>
+        <v>-7.67109740426626</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-22.4598101878753</v>
+        <v>53.6251336364091</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-4.59349168149</v>
+        <v>25.4145755648168</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>5.45212765957446</v>
+        <v>5.59774815348586</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>9.79337196112695</v>
+        <v>22.8135661133371</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>2.46262093227791</v>
+        <v>3.45450643776823</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>14.9798823893532</v>
+        <v>17.8923822341857</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -948,46 +974,46 @@
         <v>29</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>-5.80935652173913</v>
+        <v>-33.1867358005835</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>16.7211832061069</v>
+        <v>-22.490893337695</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-3.19516014234875</v>
+        <v>-4.22666190233912</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>20.3692503470616</v>
+        <v>-30.7227932559056</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-1.57817948318804</v>
+        <v>-12.4643546575309</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>19.2729570388599</v>
+        <v>8.90901301732276</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1.96046234711758</v>
+        <v>-9.1842445724895</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-7.67109740426626</v>
+        <v>15.0766359502317</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>53.6251336364091</v>
+        <v>18.6029434743287</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>25.4145755648168</v>
+        <v>8.37615030859267</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5.59774815348586</v>
+        <v>6.43184581482841</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>22.8135661133371</v>
+        <v>21.912824725965</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3.45450643776823</v>
+        <v>-5.1425384465399</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>17.8923822341857</v>
+        <v>-27.1890872940671</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -995,46 +1021,46 @@
         <v>30</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>-33.1867358005835</v>
+        <v>123.752533566795</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-22.490893337695</v>
+        <v>29.9899209537635</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-4.22666190233912</v>
+        <v>-2.69616702225322</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-30.7227932559056</v>
+        <v>38.788346107392</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-12.4643546575309</v>
+        <v>-4.7618058162603</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>8.90901301732276</v>
+        <v>13.8364799979667</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-9.1842445724895</v>
+        <v>-6.77604556977066</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>15.0766359502317</v>
+        <v>-0.16807330864077</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>18.6029434743287</v>
+        <v>-3.9709098771712</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>8.37615030859267</v>
+        <v>0.863873147876415</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>6.43184581482841</v>
+        <v>9.12445020022847</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>21.912824725965</v>
+        <v>-11.4588129158891</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>-5.1425384465399</v>
+        <v>-1.94747640761489</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>-27.1890872940671</v>
+        <v>46.4767956107763</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1042,46 +1068,46 @@
         <v>31</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>123.752533566795</v>
+        <v>-22.7953890489914</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>29.9899209537635</v>
+        <v>19.5293970790164</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-2.69616702225322</v>
+        <v>0.361604207758059</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>38.788346107392</v>
+        <v>-10.4158336665334</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-4.7618058162603</v>
+        <v>7.23297287042306</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>13.8364799979667</v>
+        <v>2.84287893496047</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-6.77604556977066</v>
+        <v>6.52268159066725</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.16807330864077</v>
+        <v>4.5212250436131</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-3.9709098771712</v>
+        <v>5.13797878567248</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.863873147876415</v>
+        <v>7.54387929793123</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>9.12445020022847</v>
+        <v>-14.4976498237368</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-11.4588129158891</v>
+        <v>3.75230372281607</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>-1.94747640761489</v>
+        <v>-1.52207850133809</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>46.4767956107763</v>
+        <v>-26.7822736030829</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1089,46 +1115,46 @@
         <v>32</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>-22.7953890489914</v>
+        <v>-14.6856502959526</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>19.5293970790164</v>
+        <v>-11.0646963605034</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.361604207758059</v>
+        <v>11.9620045856535</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-10.4158336665334</v>
+        <v>-16.6927025217585</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7.23297287042306</v>
+        <v>2.40169843867486</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2.84287893496047</v>
+        <v>7.51415857605178</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>6.52268159066725</v>
+        <v>-16.8399437620246</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>4.5212250436131</v>
+        <v>-12.0033381241597</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>5.13797878567248</v>
+        <v>18.90123020938</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>7.54387929793123</v>
+        <v>-13.4685194001428</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-14.4976498237368</v>
+        <v>24.8582717746092</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>3.75230372281607</v>
+        <v>1.79256582553442</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>-1.52207850133809</v>
+        <v>10.9267961274982</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>-26.7822736030829</v>
+        <v>42.9824561403509</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1136,46 +1162,46 @@
         <v>33</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>-14.6856502959526</v>
+        <v>14.620413775861</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-11.0646963605034</v>
+        <v>19.7671441991546</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11.9620045856535</v>
+        <v>-4.19056813527587</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-16.6927025217585</v>
+        <v>10.7709616930083</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2.40169843867486</v>
+        <v>2.0432791983414</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>7.51415857605178</v>
+        <v>-5.57576897751857</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-16.8399437620246</v>
+        <v>3.95295085978689</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-12.0033381241597</v>
+        <v>4.33477344573237</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>18.90123020938</v>
+        <v>-13.1460041568645</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-13.4685194001428</v>
+        <v>11.7376338909616</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>24.8582717746092</v>
+        <v>21.9263208585581</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>1.79256582553442</v>
+        <v>-7.96609628654621</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>10.9267961274982</v>
+        <v>14.8514265298831</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>42.9824561403509</v>
+        <v>43.4654396728016</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1183,46 +1209,46 @@
         <v>34</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>14.620413775861</v>
+        <v>8.11359070613564</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>19.7671441991546</v>
+        <v>-4.35193546268055</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>-4.19056813527587</v>
+        <v>0.935645586905221</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>10.7709616930083</v>
+        <v>-9.4817996266094</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2.0432791983414</v>
+        <v>-7.94097454144033</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-5.57576897751857</v>
+        <v>-2.50947045165952</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>3.95295085978689</v>
+        <v>2.24915616252268</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>4.33477344573237</v>
+        <v>-3.70524482975589</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-13.1460041568645</v>
+        <v>-8.46638144164119</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>11.7376338909616</v>
+        <v>-9.88761956462199</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>21.9263208585581</v>
+        <v>-2.591009190773</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-7.96609628654621</v>
+        <v>-22.6861872026392</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>14.8514265298831</v>
+        <v>-18.4902883369388</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>43.4654396728016</v>
+        <v>-0.248878904590721</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1230,46 +1256,46 @@
         <v>35</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>8.11359070613564</v>
+        <v>7.13204882477554</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-4.35193546268055</v>
+        <v>20.9522833273538</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.935645586905221</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-9.4817996266094</v>
+        <v>17.1787336361208</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-7.94097454144033</v>
+        <v>18.7089061566049</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-2.50947045165952</v>
+        <v>12.9636568002997</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>2.24915616252268</v>
+        <v>3.61859316464703</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-3.70524482975589</v>
+        <v>1.89836908070691</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-8.46638144164119</v>
+        <v>34.0017668479003</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-9.88761956462199</v>
+        <v>4.00928898299298</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-2.591009190773</v>
+        <v>-18.7210379981464</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-22.6861872026392</v>
+        <v>17.0410751573076</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>-18.4902883369388</v>
+        <v>10.8712245120489</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>-0.248878904590721</v>
+        <v>-3.0723063732495</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1277,46 +1303,46 @@
         <v>36</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>7.13204882477554</v>
+        <v>30.9705602636535</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>20.9522833273538</v>
+        <v>10.0505657019365</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>4.80665537270086</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>17.1787336361208</v>
+        <v>-55.8159826721386</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>18.7089061566049</v>
+        <v>13.0535285459757</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>12.9636568002997</v>
+        <v>-10.7343343886627</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>3.61859316464703</v>
+        <v>-29.0470086851141</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>1.89836908070691</v>
+        <v>-57.7807421131182</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>34.0017668479003</v>
+        <v>-44.8942054541946</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>4.00928898299298</v>
+        <v>-33.5212306277909</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-18.7210379981464</v>
+        <v>-7.48643814139111</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>17.0410751573076</v>
+        <v>-10.7221811128273</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>10.8712245120489</v>
+        <v>-14.8651160503541</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>-3.0723063732495</v>
+        <v>-15.6339525283798</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1324,130 +1350,84 @@
         <v>37</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30.9705602636535</v>
+        <v>15.1442617655303</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>10.0505657019365</v>
+        <v>-8.82849233214814</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4.80665537270086</v>
+        <v>4.40789994760555</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-55.8159826721386</v>
+        <v>20.9549870969307</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13.0535285459757</v>
+        <v>11.3465185883591</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-10.7343343886627</v>
+        <v>13.5688150613151</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-29.0470086851141</v>
+        <v>36.2442342935115</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-57.7807421131182</v>
+        <v>116.806621073808</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-44.8942054541946</v>
+        <v>10.9248131124949</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-33.5212306277909</v>
+        <v>20.8217170794715</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>-7.48643814139111</v>
+        <v>5.16501825713094</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-10.7221811128273</v>
+        <v>79.1753446614392</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>-14.8651160503541</v>
+        <v>34.2283817448477</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>-15.6339525283798</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+        <v>23.3715954201528</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>15.1442617655303</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>-8.82849233214814</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>4.40789994760555</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>20.9549870969307</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>11.3465185883591</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>13.5688150613151</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>36.2442342935115</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>116.806621073808</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>10.9248131124949</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>20.8217170794715</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>5.16501825713094</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>79.1753446614392</v>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>34.2283817448477</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>23.3715954201528</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-    </row>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:AB26"/>
+    <mergeCell ref="A25:AB25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
